--- a/business_surveys/038_social_care_collaboration_effectiveness_survey--business_surveys.xlsx
+++ b/business_surveys/038_social_care_collaboration_effectiveness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>introduction_question_1</t>
+          <t>collaboration_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>introduction_question_2</t>
+          <t>communication_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>introduction_question_3</t>
+          <t>team_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>introduction_question_4</t>
+          <t>collaboration_effectiveness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>role_in_team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Section 2</t>
+          <t>What is your role in the team?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>section_2_question_1</t>
+          <t>section_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How important is it for you to have a team that supports you?</t>
+          <t>Section 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>section_2_question_2</t>
+          <t>meeting_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How important is it for you to have a clear plan for your work?</t>
+          <t>How often do you meet with your team?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>introduction_question_5</t>
+          <t>team_resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your role in the team?</t>
+          <t>Do you feel like your team has the resources they need to do their work?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>introduction_question_6</t>
+          <t>decision_making_process</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you meet with your team?</t>
+          <t>How satisfied are you with the team's decision-making process?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>introduction_question_7</t>
+          <t>communication_style</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often do you communicate with your team?</t>
+          <t>Do you feel like the team's communication style is effective?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>introduction_question_8</t>
+          <t>trust_in_team</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How satisfied are you with the way your team works together?</t>
+          <t>How often do you feel like you can trust your team?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>introduction_question_9</t>
+          <t>collaboration_frequency_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How satisfied are you with your role in the team?</t>
+          <t>Collaboration Frequency 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>introduction_question_10</t>
+          <t>performance_satisfaction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Do you feel like you can rely on your team to follow through on their commitments?</t>
+          <t>How satisfied are you with the team's performance?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>introduction_question_11</t>
+          <t>feedback_openness</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How satisfied are you with the way the team works together?</t>
+          <t>Do you feel like your team is open to feedback?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>introduction_question_12</t>
+          <t>communication_frequency_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How important is it for you to have a clear plan for your work?</t>
+          <t>Communication Frequency 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,200 +888,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>introduction_question_13</t>
+          <t>section_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How often do you meet with your team?</t>
+          <t>Section 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>introduction_question_14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Do you feel like your team has the resources they need to do their work?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>introduction_question_15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How satisfied are you with the team's decision-making process?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>introduction_question_16</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Do you feel like the team's communication style is effective?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>introduction_question_17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How often do you feel like you can trust your team?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>introduction_question_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How often do you collaborate with your team?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>introduction_question_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How satisfied are you with the team's performance?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>introduction_question_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Do you feel like your team is open to feedback?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>introduction_question_21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How often do you communicate with your team?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +914,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +942,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>introduction_question_3_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +959,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>introduction_question_3_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +976,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>introduction_question_3_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,24 +993,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>introduction_question_3_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>somewhat_unsupported</t>
+          <t>somewhat_not_supported</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Somewhat unsupported</t>
+          <t>Somewhat not supported</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>introduction_question_3_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1027,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>introduction_question_4_choices</t>
+          <t>collaboration_effectiveness_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>introduction_question_4_choices</t>
+          <t>collaboration_effectiveness_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1061,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>introduction_question_4_choices</t>
+          <t>collaboration_effectiveness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1078,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>introduction_question_4_choices</t>
+          <t>collaboration_effectiveness_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,24 +1095,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>introduction_question_4_choices</t>
+          <t>collaboration_effectiveness_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_effective_at_all</t>
+          <t>not_at_all_effective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not effective at all</t>
+          <t>Not at all effective</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>introduction_question_5_choices</t>
+          <t>role_in_team_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1129,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>introduction_question_5_choices</t>
+          <t>role_in_team_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1146,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>introduction_question_5_choices</t>
+          <t>role_in_team_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1163,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>introduction_question_5_choices</t>
+          <t>role_in_team_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,41 +1180,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>introduction_question_8_choices</t>
+          <t>team_resources_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>i_feel_fully_supported</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>I feel fully supported</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>introduction_question_8_choices</t>
+          <t>team_resources_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>i_feel_somewhat_supported</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Somewhat satisfied</t>
+          <t>I feel somewhat supported</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>introduction_question_8_choices</t>
+          <t>team_resources_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,41 +1231,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>introduction_question_8_choices</t>
+          <t>team_resources_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>i_feel_somewhat_not_supported</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Somewhat dissatisfied</t>
+          <t>I feel somewhat not supported</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>introduction_question_8_choices</t>
+          <t>team_resources_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>i_feel_not_at_all_supported</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>I feel not at all supported</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>introduction_question_9_choices</t>
+          <t>decision_making_process_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1282,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>introduction_question_9_choices</t>
+          <t>decision_making_process_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1299,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>introduction_question_9_choices</t>
+          <t>decision_making_process_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1316,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>introduction_question_9_choices</t>
+          <t>decision_making_process_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1333,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>introduction_question_9_choices</t>
+          <t>decision_making_process_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,41 +1350,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>introduction_question_10_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i_can_fully_rely_on_them</t>
+          <t>i_feel_it_is_very_effective</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>I can fully rely on them</t>
+          <t>I feel it is very effective</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>introduction_question_10_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i_can_somewhat_rely_on_them</t>
+          <t>i_feel_it_is_somewhat_effective</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>I can somewhat rely on them</t>
+          <t>I feel it is somewhat effective</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>introduction_question_10_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,41 +1401,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>introduction_question_10_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i_can_somewhat_not_rely_on_them</t>
+          <t>i_feel_it_is_somewhat_not_effective</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>I can somewhat not rely on them</t>
+          <t>I feel it is somewhat not effective</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>introduction_question_10_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i_can_not_at_all_rely_on_them</t>
+          <t>i_feel_it_is_not_at_all_effective</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>I can not at all rely on them</t>
+          <t>I feel it is not at all effective</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>introduction_question_11_choices</t>
+          <t>performance_satisfaction_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1452,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>introduction_question_11_choices</t>
+          <t>performance_satisfaction_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1469,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>introduction_question_11_choices</t>
+          <t>performance_satisfaction_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1486,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>introduction_question_11_choices</t>
+          <t>performance_satisfaction_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1503,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>introduction_question_11_choices</t>
+          <t>performance_satisfaction_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,41 +1520,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>introduction_question_14_choices</t>
+          <t>feedback_openness_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i_feel_fully_supported</t>
+          <t>i_feel_fully_open</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>I feel fully supported</t>
+          <t>I feel fully open</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>introduction_question_14_choices</t>
+          <t>feedback_openness_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>i_feel_somewhat_supported</t>
+          <t>i_feel_somewhat_open</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>I feel somewhat supported</t>
+          <t>I feel somewhat open</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>introduction_question_14_choices</t>
+          <t>feedback_openness_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,372 +1571,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>introduction_question_14_choices</t>
+          <t>feedback_openness_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>i_feel_somewhat_not_supported</t>
+          <t>i_feel_somewhat_not_open</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>I feel somewhat not supported</t>
+          <t>I feel somewhat not open</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>introduction_question_14_choices</t>
+          <t>feedback_openness_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>i_feel_not_at_all_supported</t>
+          <t>i_feel_not_at_all_open</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
-        <is>
-          <t>I feel not at all supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>introduction_question_15_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>introduction_question_15_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>somewhat_satisfied</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Somewhat satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>introduction_question_15_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>introduction_question_15_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>somewhat_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Somewhat dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>introduction_question_15_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Very dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>introduction_question_16_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>i_feel_it_is_very_effective</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>I feel it is very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>introduction_question_16_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>i_feel_it_is_somewhat_effective</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>I feel it is somewhat effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>introduction_question_16_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>introduction_question_16_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>i_feel_it_is_somewhat_not_effective</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>I feel it is somewhat not effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>introduction_question_16_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>i_feel_it_is_not_at_all_effective</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>I feel it is not at all effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>introduction_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>introduction_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>somewhat_satisfied</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Somewhat satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>introduction_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>introduction_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>somewhat_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Somewhat dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>introduction_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Very dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>introduction_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>i_feel_fully_open</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>I feel fully open</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>introduction_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>i_feel_somewhat_open</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>I feel somewhat open</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>introduction_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>introduction_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>i_feel_somewhat_not_open</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>I feel somewhat not open</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>introduction_question_20_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>i_feel_not_at_all_open</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>I feel not at all open</t>
         </is>
